--- a/Destaques Q3.xlsx
+++ b/Destaques Q3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Claro\Encontro Mensal\Q32025\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Replit\DestaqueVotacao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{215DE2C9-0743-451E-A958-59E28256A818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A19E8A0B-0C0C-49D3-BEEE-0B186DACCDD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{0DBA62B0-DE08-455D-A6EB-3569383BDBAE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{0DBA62B0-DE08-455D-A6EB-3569383BDBAE}"/>
   </bookViews>
   <sheets>
     <sheet name="INDICADOS" sheetId="2" r:id="rId1"/>
@@ -213,7 +213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -222,9 +222,6 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -381,15 +378,15 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C4EC71B6-401F-4780-B0C9-60CC310B6431}" name="Tabela1" displayName="Tabela1" ref="A1:F13" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
   <autoFilter ref="A1:F13" xr:uid="{C4EC71B6-401F-4780-B0C9-60CC310B6431}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F13">
-    <sortCondition ref="F1:F13"/>
+    <sortCondition ref="A1:A13"/>
   </sortState>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{23737FEC-D68B-4EDD-97F3-A64CB72C9F65}" name="COLABORADOR" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{4FEB5BE2-EDBD-440A-906A-5FEE8AD2A7F2}" name="GESTOR" dataDxfId="0"/>
-    <tableColumn id="2" xr3:uid="{F3F79E8D-C136-4E9C-BA66-ED1EDB31AD83}" name="JUSTIFICATIVA" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{0B8F03B9-5B42-4114-A0D7-6883DC6A2A38}" name="PERIODO" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{D72605FF-670B-4422-8A15-B54D290F84FB}" name="CATEGORIA" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{88B949EC-41BB-489D-BDBD-32CDE1EABF6E}" name="ÁREA" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{4FEB5BE2-EDBD-440A-906A-5FEE8AD2A7F2}" name="GESTOR" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{F3F79E8D-C136-4E9C-BA66-ED1EDB31AD83}" name="JUSTIFICATIVA" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{0B8F03B9-5B42-4114-A0D7-6883DC6A2A38}" name="PERIODO" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{D72605FF-670B-4422-8A15-B54D290F84FB}" name="CATEGORIA" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{88B949EC-41BB-489D-BDBD-32CDE1EABF6E}" name="ÁREA" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -713,17 +710,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27300FAB-3D0A-48B8-B64D-F8F7B39556B7}">
   <dimension ref="A1:F13"/>
-  <sheetFormatPr defaultColWidth="26.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="26.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.08984375" style="1"/>
-    <col min="2" max="2" width="16.08984375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="26.140625" style="1"/>
+    <col min="2" max="2" width="16.140625" style="1" customWidth="1"/>
     <col min="3" max="3" width="25" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.36328125" customWidth="1"/>
-    <col min="5" max="5" width="27.453125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="26.08984375" style="1"/>
+    <col min="4" max="4" width="10.42578125" customWidth="1"/>
+    <col min="5" max="5" width="27.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="26.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -743,8 +740,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
         <v>31</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -763,106 +760,103 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="13" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>32</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="13" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="13" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="13" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="13" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>9</v>
@@ -871,15 +865,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="13" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>23</v>
+    <row r="9" spans="1:6" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>9</v>
@@ -888,32 +882,32 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="13" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
+    <row r="10" spans="1:6" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="13" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>9</v>
@@ -922,15 +916,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>9</v>
@@ -938,22 +932,25 @@
       <c r="E12" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" ht="13" x14ac:dyDescent="0.3">
+      <c r="F12" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/Destaques Q3.xlsx
+++ b/Destaques Q3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Replit\DestaqueVotacao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A19E8A0B-0C0C-49D3-BEEE-0B186DACCDD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF69852B-7680-4FD1-B49D-A4B7560BBA2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{0DBA62B0-DE08-455D-A6EB-3569383BDBAE}"/>
   </bookViews>
